--- a/iFST_online_PsychoPy/ifst_files/self_assess_questions.xlsx
+++ b/iFST_online_PsychoPy/ifst_files/self_assess_questions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github_repos/iFST/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uclouvain-my.sharepoint.com/personal/marcos_morenoverdu_uclouvain_be/Documents/BAS-Lab/Github repositories/iFST/iFST_local_PsychoPy/ifst_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="179" documentId="13_ncr:1_{7C03145D-33C7-4180-AD68-8649CE308F0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C748BD24-093C-43D9-AC0E-7B72CE15BF64}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{BF97F26B-3F63-411C-8CFB-C96FB465EA62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E0D980E-EBDA-4769-99CC-136B8465E04C}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -440,9 +440,6 @@
     <t>Nur eine visuelle Modalität</t>
   </si>
   <si>
-    <t>Kein Bild überhaupt, Sie „wussten“ nur, dass Sie an die Bewegung gedacht haben</t>
-  </si>
-  <si>
     <t>Keine Fehler, ich war während der Vorstellung vollständig korrekt</t>
   </si>
   <si>
@@ -458,68 +455,71 @@
     <t>Keine Nutzung kinästhetischer Vorstellung</t>
   </si>
   <si>
-    <t>Bitte beantworten Sie die folgenden Fragen zur Vorstellung, die Sie im LETZTEN Block ausgeführt haben.
+    <t>Wie lebhaft war die Vorstellung der Bewegung INSGESAMT (unter Berücksichtigung SOWOHL der Klarheit des Bildes ALS AUCH der Intensität der Empfindungen)? Wählen Sie nur dann 0, wenn Sie überhaupt nichts gesehen oder gefühlt haben.</t>
+  </si>
+  <si>
+    <t>Haben Sie sich beim Vorstellen der Bewegung Fehler vorgestellt (z. B. die falsche Taste gedrückt)? Wählen Sie nur dann 0, wenn Sie sich im GESAMTEN BLOCK KEINE FEHLER vorgestellt haben.</t>
+  </si>
+  <si>
+    <t>Wie stark haben Sie beim Vorstellen der Bewegung die VISUELLE MODALITÄT der Vorstellung genutzt (ein visuelles Bild der Bewegung erzeugt)? Wählen Sie nur dann „0“, wenn Sie visuelle Vorstellung überhaupt nicht genutzt haben.</t>
+  </si>
+  <si>
+    <t>Falls Sie visuelle Vorstellung genutzt haben: Haben Sie eine ERSTE-PERSON-PERSPEKTIVE verwendet (die Bewegung durch die Augen der ausführenden Person gesehen, aus einer internen Perspektive)? Wenn Sie in der vorherigen Frage 0 gewählt haben, müssen Sie hier ebenfalls 0 wählen.</t>
+  </si>
+  <si>
+    <t>Falls Sie visuelle Vorstellung genutzt haben: Haben Sie eine DRITTE-PERSON-PERSPEKTIVE verwendet (sich selbst bei der Ausführung der Bewegung beobachtet, aus einer externen Perspektive)? Wenn Sie in der Frage zur allgemeinen Nutzung visueller Vorstellung 0 gewählt haben, müssen Sie hier ebenfalls 0 wählen.</t>
+  </si>
+  <si>
+    <t>Wie stark haben Sie beim Vorstellen der Bewegung die KINÄSTHETISCHE MODALITÄT der Vorstellung genutzt (die Empfindungen der Bewegung gespürt)? Wählen Sie nur dann „0“, wenn Sie kinästhetische Vorstellung überhaupt nicht genutzt haben.</t>
+  </si>
+  <si>
+    <t>label_max_DE</t>
+  </si>
+  <si>
+    <t>label_middle_DE</t>
+  </si>
+  <si>
+    <t>Nur eine kinästhetische Modalität</t>
+  </si>
+  <si>
+    <t>Vollkommen klar und lebhaft, wie normales Sehen und/oder das normale Gefühl einer Bewegung</t>
+  </si>
+  <si>
+    <t>Viele Fehler, ich war während der Vorstellung völlig ungenau</t>
+  </si>
+  <si>
+    <t>Beide Modalitäten
+gleichzeitig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   </t>
+  </si>
+  <si>
+    <t>Bitte beantworten Sie die folgenden Fragen zu Ihrer Vorstellung im LETZTEN Block.
 Verwenden Sie die Maus.
 Im letzten Block lautete die ANWEISUNG beim VORSTELLEN der Bewegung, folgende Modalität zu verwenden:</t>
   </si>
   <si>
-    <t>Wie lebhaft war die Vorstellung der Bewegung INSGESAMT (unter Berücksichtigung SOWOHL der Klarheit des Bildes ALS AUCH der Intensität der Empfindungen)? Wählen Sie nur dann 0, wenn Sie überhaupt nichts gesehen oder gefühlt haben.</t>
-  </si>
-  <si>
-    <t>Haben Sie sich beim Vorstellen der Bewegung Fehler vorgestellt (z. B. die falsche Taste gedrückt)? Wählen Sie nur dann 0, wenn Sie sich im GESAMTEN BLOCK KEINE FEHLER vorgestellt haben.</t>
-  </si>
-  <si>
-    <t>Wie stark haben Sie beim Vorstellen der Bewegung die VISUELLE MODALITÄT der Vorstellung genutzt (ein visuelles Bild der Bewegung erzeugt)? Wählen Sie nur dann „0“, wenn Sie visuelle Vorstellung überhaupt nicht genutzt haben.</t>
-  </si>
-  <si>
-    <t>Falls Sie visuelle Vorstellung genutzt haben: Haben Sie eine ERSTE-PERSON-PERSPEKTIVE verwendet (die Bewegung durch die Augen der ausführenden Person gesehen, aus einer internen Perspektive)? Wenn Sie in der vorherigen Frage 0 gewählt haben, müssen Sie hier ebenfalls 0 wählen.</t>
-  </si>
-  <si>
-    <t>Falls Sie visuelle Vorstellung genutzt haben: Haben Sie eine DRITTE-PERSON-PERSPEKTIVE verwendet (sich selbst bei der Ausführung der Bewegung beobachtet, aus einer externen Perspektive)? Wenn Sie in der Frage zur allgemeinen Nutzung visueller Vorstellung 0 gewählt haben, müssen Sie hier ebenfalls 0 wählen.</t>
-  </si>
-  <si>
-    <t>Wie stark haben Sie beim Vorstellen der Bewegung die KINÄSTHETISCHE MODALITÄT der Vorstellung genutzt (die Empfindungen der Bewegung gespürt)? Wählen Sie nur dann „0“, wenn Sie kinästhetische Vorstellung überhaupt nicht genutzt haben.</t>
-  </si>
-  <si>
-    <t>label_max_DE</t>
-  </si>
-  <si>
-    <t>label_middle_DE</t>
-  </si>
-  <si>
-    <t>Nur eine kinästhetische Modalität</t>
-  </si>
-  <si>
-    <t>Vollkommen klar und lebhaft, wie normales Sehen und/oder das normale Gefühl einer Bewegung</t>
-  </si>
-  <si>
-    <t>Viele Fehler, ich war während der Vorstellung völlig ungenau</t>
-  </si>
-  <si>
-    <t>Hohe Nutzung visueller Vorstellung</t>
-  </si>
-  <si>
-    <t>Hohe Nutzung der Ich-Perspektive (intern)</t>
-  </si>
-  <si>
-    <t>Hohe Nutzung der Dritte-Person-Perspektive (extern)</t>
-  </si>
-  <si>
-    <t>Hohe Nutzung kinästhetischer Vorstellung</t>
-  </si>
-  <si>
-    <t>Beide Modalitäten
-gleichzeitig</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   </t>
+    <t>Überhaupt kein Bild, Sie „wussten“ nur, dass Sie an die Bewegung gedacht haben</t>
+  </si>
+  <si>
+    <t>Starke Nutzung visueller Vorstellung</t>
+  </si>
+  <si>
+    <t>Starke Nutzung der Ich-Perspektive (intern)</t>
+  </si>
+  <si>
+    <t>Starke Nutzung der Dritte-Person-Perspektive (extern)</t>
+  </si>
+  <si>
+    <t>Starke Nutzung kinästhetischer Vorstellung</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -550,6 +550,12 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -577,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -590,6 +596,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -613,10 +625,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -917,72 +925,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="20.7265625" defaultRowHeight="20.25" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15.36328125" customWidth="1"/>
+    <col min="1" max="1" width="22.453125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.08984375" customWidth="1"/>
     <col min="5" max="5" width="23.453125" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" customWidth="1"/>
-    <col min="7" max="7" width="14.08984375" customWidth="1"/>
-    <col min="8" max="8" width="16.26953125" customWidth="1"/>
+    <col min="6" max="6" width="13.6328125" customWidth="1"/>
+    <col min="7" max="7" width="13.90625" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" customWidth="1"/>
     <col min="9" max="9" width="22.26953125" customWidth="1"/>
-    <col min="10" max="10" width="17.54296875" customWidth="1"/>
-    <col min="12" max="12" width="14.7265625" customWidth="1"/>
+    <col min="10" max="10" width="17.26953125" customWidth="1"/>
+    <col min="11" max="11" width="16.6328125" customWidth="1"/>
+    <col min="12" max="12" width="14.08984375" customWidth="1"/>
+    <col min="13" max="13" width="20.6328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="20.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>96</v>
+      <c r="O1" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
         <v>30</v>
       </c>
@@ -1019,20 +1032,20 @@
       <c r="L2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="M2" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="N2" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="O2" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="P2" t="s">
-        <v>98</v>
+      <c r="O2" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="174" x14ac:dyDescent="0.35">
       <c r="A3" s="4" t="s">
         <v>20</v>
       </c>
@@ -1069,20 +1082,20 @@
       <c r="L3" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="M3" t="s">
-        <v>90</v>
-      </c>
-      <c r="N3" t="s">
-        <v>83</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="P3" t="s">
-        <v>99</v>
+      <c r="M3" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P3" s="6" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>21</v>
       </c>
@@ -1095,7 +1108,7 @@
       <c r="D4" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>61</v>
       </c>
       <c r="F4" s="3" t="s">
@@ -1107,7 +1120,7 @@
       <c r="H4" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="3" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -1119,21 +1132,21 @@
       <c r="L4" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="M4" t="s">
-        <v>91</v>
-      </c>
-      <c r="N4" t="s">
-        <v>84</v>
-      </c>
-      <c r="O4" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="P4" t="s">
+      <c r="M4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="O4" s="6" t="s">
         <v>100</v>
       </c>
+      <c r="P4" s="6" t="s">
+        <v>98</v>
+      </c>
     </row>
-    <row r="5" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:16" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -1145,7 +1158,7 @@
       <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>65</v>
       </c>
       <c r="F5" s="3" t="s">
@@ -1157,7 +1170,7 @@
       <c r="H5" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="3" t="s">
         <v>35</v>
       </c>
       <c r="J5" s="3" t="s">
@@ -1169,21 +1182,21 @@
       <c r="L5" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="M5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N5" t="s">
-        <v>85</v>
-      </c>
-      <c r="O5" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="P5" t="s">
-        <v>101</v>
+      <c r="M5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P5" s="6" t="s">
+        <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:16" ht="232" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -1195,7 +1208,7 @@
       <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>62</v>
       </c>
       <c r="F6" s="3" t="s">
@@ -1207,7 +1220,7 @@
       <c r="H6" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="I6" t="s">
+      <c r="I6" s="3" t="s">
         <v>36</v>
       </c>
       <c r="J6" s="3" t="s">
@@ -1219,21 +1232,21 @@
       <c r="L6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="M6" t="s">
-        <v>93</v>
-      </c>
-      <c r="N6" t="s">
-        <v>86</v>
-      </c>
-      <c r="O6" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="P6" t="s">
-        <v>102</v>
+      <c r="M6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P6" s="6" t="s">
+        <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:16" ht="232" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1245,7 +1258,7 @@
       <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>63</v>
       </c>
       <c r="F7" s="3" t="s">
@@ -1257,7 +1270,7 @@
       <c r="H7" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I7" t="s">
+      <c r="I7" s="3" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="3" t="s">
@@ -1269,21 +1282,21 @@
       <c r="L7" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="M7" t="s">
-        <v>94</v>
-      </c>
-      <c r="N7" t="s">
-        <v>87</v>
-      </c>
-      <c r="O7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="P7" t="s">
-        <v>103</v>
+      <c r="M7" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>105</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:16" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -1295,7 +1308,7 @@
       <c r="D8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="3" t="s">
@@ -1307,7 +1320,7 @@
       <c r="H8" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="I8" t="s">
+      <c r="I8" s="3" t="s">
         <v>54</v>
       </c>
       <c r="J8" s="3" t="s">
@@ -1319,17 +1332,17 @@
       <c r="L8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="M8" t="s">
-        <v>95</v>
-      </c>
-      <c r="N8" t="s">
-        <v>88</v>
-      </c>
-      <c r="O8" s="3" t="s">
+      <c r="M8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="P8" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="P8" t="s">
-        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -1345,6 +1358,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100B9F5CAB0486A994CA2C3B13E059EF2AE" ma:contentTypeVersion="0" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="8645ec4a60d0c8c7009d2d6675847a91">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="636d7205651659ec4fcda0bcbde9384b">
     <xsd:element name="properties">
@@ -1458,38 +1486,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3725960-8A89-4E70-9C40-340E0EDB6403}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
@@ -1504,10 +1501,26 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3744155D-8FAB-4E67-B5E0-C7FDBFB3715D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EFF1C174-6AC6-4774-A736-3226A12360E4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>